--- a/MU/Test upload format/SHG/2026 - 2027 - SHG/Update CG Q2.xlsx
+++ b/MU/Test upload format/SHG/2026 - 2027 - SHG/Update CG Q2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>custid</t>
   </si>
@@ -86,10 +86,13 @@
     <t>modifiedloancat</t>
   </si>
   <si>
-    <t>Envv16</t>
-  </si>
-  <si>
-    <t>Envv17</t>
+    <t>HomeStay</t>
+  </si>
+  <si>
+    <t>XSHG0124234</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
   <si>
     <t>Y</t>
@@ -98,22 +101,19 @@
     <t>01-07-2026</t>
   </si>
   <si>
+    <t>100000</t>
+  </si>
+  <si>
     <t>01-04-2026</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>Envv18</t>
-  </si>
-  <si>
-    <t>IA</t>
-  </si>
-  <si>
-    <t>K</t>
+    <t>900001</t>
+  </si>
+  <si>
+    <t>SHG</t>
   </si>
 </sst>
 </file>
@@ -481,27 +481,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -626,7 +611,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -638,34 +623,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -752,23 +737,21 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1119,165 +1102,135 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2"/>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="11.8571428571429" customWidth="1"/>
-    <col min="4" max="4" width="9.42857142857143" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1428571428571" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.4285714285714" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.1428571428571" style="3" customWidth="1"/>
     <col min="6" max="6" width="24.4285714285714" customWidth="1"/>
-    <col min="7" max="7" width="23.1428571428571" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.1428571428571" style="3" customWidth="1"/>
     <col min="8" max="8" width="16.1428571428571" customWidth="1"/>
-    <col min="9" max="9" width="15" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15" style="3" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
     <col min="11" max="11" width="11.8571428571429" customWidth="1"/>
     <col min="12" max="12" width="14.5714285714286" customWidth="1"/>
     <col min="13" max="13" width="24.8571428571429" customWidth="1"/>
-    <col min="14" max="14" width="22" style="2" customWidth="1"/>
+    <col min="14" max="14" width="22" style="3" customWidth="1"/>
+    <col min="16" max="16" width="17.1428571428571" customWidth="1"/>
+    <col min="17" max="17" width="18.1428571428571" customWidth="1"/>
+    <col min="18" max="18" width="26.4285714285714" customWidth="1"/>
+    <col min="19" max="19" width="18.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:20">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" customFormat="1" spans="1:19">
-      <c r="A2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="7" t="s">
+    <row r="2" customFormat="1" spans="1:20">
+      <c r="A2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="8">
-        <v>1000</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="D2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="8">
-        <v>9000</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>23</v>
       </c>
+      <c r="F2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="H2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="7"/>
+        <v>26</v>
+      </c>
+      <c r="I2" s="8"/>
       <c r="J2"/>
-      <c r="K2" s="7">
+      <c r="K2" s="8">
         <v>0</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="8">
         <v>1</v>
       </c>
-      <c r="M2" s="9">
-        <v>100000</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>23</v>
+      <c r="M2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="S2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" customFormat="1" spans="1:19">
-      <c r="A3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" t="s">
         <v>26</v>
-      </c>
-      <c r="C3" s="8">
-        <v>1000</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8">
-        <v>9000</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="K3" s="7">
-        <v>0</v>
-      </c>
-      <c r="L3" s="7">
-        <v>1</v>
-      </c>
-      <c r="M3" s="9">
-        <v>100000</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="S3" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
